--- a/Server/reports/qc_report.xlsx
+++ b/Server/reports/qc_report.xlsx
@@ -49,10 +49,10 @@
       <sz val="11"/>
     </font>
     <font>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
       <color rgb="00276221"/>
-    </font>
-    <font>
-      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -90,7 +90,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00276221"/>
+      <color rgb="009C0006"/>
       <sz val="14"/>
     </font>
     <font>
@@ -185,16 +185,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,10 +233,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-27 16:35 UTC</t>
+          <t>2026-04-29 05:45 UTC</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -672,9 +672,21 @@
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>88.9%</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Weighted Score</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -760,14 +772,22 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Analysis could not be completed automatically.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Manual review required.</t>
+        </is>
+      </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr"/>
@@ -786,18 +806,30 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr"/>
-      <c r="E3" s="9" t="inlineStr"/>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>The project description should be updated to include the exact IDs and types for the input fields, select field, checkbox, and submit button, such as 'id="albumName" type="text"', 'id="releaseYear" type="number"', 'id="genre"', 'id="favorite" type="checkbox"', and 'id="addAlbumBtn" type="button"'.</t>
+        </is>
+      </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr"/>
-      <c r="H3" s="9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>The project description does not explicitly mention the exact IDs 'albumName', 'releaseYear', 'genre', 'favorite', and 'addAlbumBtn' used in the test code. It only mentions 'an album name input field', 'a release year input field', 'a genre select field', 'a favorite checkbox', and 'a submit button' without specifying the exact IDs or types.</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>The test code is checking for specific IDs and types, but the generated HTML uses different IDs ('album-name', 'release-year', etc.) and the project description does not specify the exact IDs or types.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -812,18 +844,30 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="9" t="inlineStr"/>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Add the exact ID 'addAlbumBtn' and the background color 'rgb(76, 175, 80)' to the project description to specify the required styling for the submit button.</t>
+        </is>
+      </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>The project description never mentions the exact ID 'addAlbumBtn' or the background color 'rgb(76, 175, 80)' for the button. It only mentions a submit button without specifying its ID or styling.</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>button { padding: 10px; margin: 0 10px; }</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -838,86 +882,97 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>The project description should be updated to include the exact ID 'addAlbumBtn' and the text 'Add Album' for the submit button, for example: 'The form includes a submit button with the ID "addAlbumBtn" and the text "Add Album".'</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>The project description does not explicitly mention the ID 'addAlbumBtn' or the exact text 'Add Album' for the submit button. The description only mentions 'a submit button' without specifying the ID or the exact text.</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>button type="submit"&gt;Add Album&lt;/button&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>verify_placeholder_and_label_texts</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Verify Placeholder And Label Texts</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>The project description should be updated to include the exact label texts and placeholder texts that the test checks for, such as 'The form should have labels with the exact texts: Album Name:, Release Year:, Genre:, and Mark as Favorite:', and 'The album name input field should have a placeholder text of Enter album name, and the release year input field should have a placeholder text of Enter release year'.</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>The project description does not explicitly mention the exact label texts ('Album Name:', 'Release Year:', 'Genre:', 'Mark as Favorite') and placeholder texts ('Enter album name', 'Enter release year') that the test checks for. It only mentions that users can enter an album name and release year, select a genre, and optionally mark an album as a favorite, without specifying the exact wording of the labels and placeholders.</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>label for="album-name"&gt;Album Name:&lt;/label&gt;
+label for="release-year"&gt;Release Year:&lt;/label&gt;
+label for="genre"&gt;Genre:&lt;/label&gt;
+label for="favorite"&gt;Favorite:&lt;/label&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>verify_page_title</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Verify Page Title</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>verify_placeholder_and_label_texts</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Verify Placeholder And Label Texts</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>The generated HTML code does not include placeholder attributes for the input fields, and the label texts do not match the expected texts in the test code block.</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Update the project description to include the exact placeholder text for the input fields and the exact label text for the labels. Then, update the generated HTML code to include the placeholder attributes for the input fields and the correct label texts.</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>The project description does not specify the exact placeholder text for the input fields (albumName and releaseYear) and the exact label text for the labels (albumName, releaseYear, genre, and favorite). The test code block checks for specific placeholder and label texts, but these are not mentioned in the project description.</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>The relevant code snippet from the generated HTML is: &lt;label for="albumName"&gt;Album Name:&lt;/label&gt; &lt;input type="text" id="albumName" required&gt; and &lt;label for="releaseYear"&gt;Release Year:&lt;/label&gt; &lt;input type="number" id="releaseYear" required&gt;. The placeholder attributes are missing, and the label texts do not match the expected texts in the test code block.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>verify_page_title</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Verify Page Title</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="G7" s="11" t="inlineStr"/>
+      <c r="H7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -932,18 +987,32 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>The project description should be updated to include the exact IDs and error message used in the test code, as well as the initial state of the album lists and error message.</t>
+        </is>
+      </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>The project description does not mention the exact IDs 'albumList', 'favoriteAlbumList', 'addAlbumBtn', or 'error-message' used in the test code. It also does not specify the exact error message 'Please fill out all fields!' or the initial state of the album lists and error message.</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>const initialAlbumListContent = await page6.$eval('#albumList', el =&gt; el.textContent.trim());
+const initialFavoriteListContent = await page6.$eval('#favoriteAlbumList', el =&gt; el.textContent.trim());
+const initialErrorMessage = await page6.$eval('#error-message', el =&gt; el.textContent.trim());</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -958,18 +1027,30 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>The project description should explicitly mention the exact IDs 'album-name', 'release-year', 'genre', and 'favorite' used in the HTML code, or the test code should be updated to use the correct IDs.</t>
+        </is>
+      </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>The project description does not explicitly mention the exact IDs 'albumName', 'releaseYear', 'genre', and 'favorite' used in the test code. It only mentions 'an album name input field', 'a release year input field', 'a genre select field', and 'a favorite checkbox' without specifying the exact IDs.</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>The test code uses IDs 'albumName', 'releaseYear', 'genre', and 'favorite', but the HTML code uses IDs 'album-name', 'release-year', 'genre', and 'favorite'.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -984,18 +1065,30 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>The project description should explicitly mention the exact IDs 'albumName', 'releaseYear', and 'genre' or specify the structure of the form fields to match the test code.</t>
+        </is>
+      </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>The project description does not explicitly mention the exact IDs 'albumName', 'releaseYear', and 'genre' used in the test code. It only mentions 'album name', 'release year', and 'genre' in a general sense, without specifying the exact IDs or the structure of the form fields.</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>The test code uses IDs 'albumName', 'releaseYear', and 'genre' which are not present in the generated HTML. Instead, the generated HTML uses IDs 'album-name', 'release-year', and 'genre'.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1058,22 +1151,22 @@
       <c r="A3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>No issues. Publish-ready.</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>None required</t>
         </is>
@@ -1158,22 +1251,22 @@
       <c r="A7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>D only</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Complete failure. If ★ Critical → Grade D.</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Reject / recreate</t>
         </is>
@@ -1218,72 +1311,72 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Milestone / Deliverable Def.</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>The project stages or milestones are clearly defined with measurable acceptance criteria, including specific input fields, validation, and display requirements.</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>None required</t>
+      <c r="C10" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Needs Work</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>C/D</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>The project lacks clear definition of milestones or deliverables with measurable acceptance criteria.</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>Define specific project stages with clear deliverables and acceptance criteria.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Expected Output Clarity</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>The final deliverable is described with concrete examples and acceptance criteria, including sample output and specific functionality.</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>None required</t>
+      <c r="C11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>The final deliverable is described with a clear functionality but lacks concrete examples.</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Provide concrete examples of the expected output, such as a sample album collection list.</t>
         </is>
       </c>
     </row>
@@ -1298,62 +1391,62 @@
           <t>★ Critical</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>5</v>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Excellent</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D only</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Complete step-by-step instructions are provided for setup, run, test, and submit, including specific commands and port numbers.</t>
+          <t>There are no step-by-step instructions provided for setup, run, test, or submission of the project.</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>None required</t>
+          <t>Provide complete step-by-step instructions for all phases of the project.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Difficulty vs Effort Calibration</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>The project scope is mostly realistic for the stated difficulty level and time allocation, but may require some additional effort for testing and debugging.</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>Consider adding more time for testing and debugging</t>
+      <c r="C13" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>B/C</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>The project scope seems manageable but lacks clear information on the expected difficulty level and time allocation.</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>Specify the expected difficulty level and time allocation for the project to ensure realistic scope calibration.</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1458,19 @@
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>Total Score: 19/20</t>
+          <t>Total Score: 10/20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>The project description is well-structured and provides clear requirements, functionality, and instructions. The scope is mostly realistic, and the project can be completed with some effort. Overall, the project description meets the highest standards and is publish-ready.</t>
+          <t>The project description lacks critical details such as milestones, step-by-step instructions, and scope calibration, resulting in a failing grade. Significant revisions are required to meet the project standards.</t>
         </is>
       </c>
     </row>
